--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate/AGGREGATE_JAEN PARAISO INTERIOR FS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate/AGGREGATE_JAEN PARAISO INTERIOR FS.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>165.88</v>
+        <v>413.9599999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>165.12</v>
+        <v>414.56</v>
       </c>
       <c r="D2" t="n">
-        <v>119.9127906976744</v>
+        <v>110.9610189116171</v>
       </c>
       <c r="E2" t="n">
-        <v>95.08236434108527</v>
+        <v>96.48784253184098</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.4818435754189944</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1040221914008322</v>
+        <v>0.1491172260219501</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4044943820224719</v>
+        <v>0.3938053097345133</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2531645569620253</v>
+        <v>0.3212290502793296</v>
       </c>
       <c r="J2" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K2" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="L2" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="M2" t="n">
+        <v>36</v>
+      </c>
+      <c r="N2" t="n">
+        <v>85</v>
+      </c>
+      <c r="O2" t="n">
+        <v>157</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.4385474860335196</v>
+      </c>
+      <c r="Q2" t="n">
         <v>8</v>
       </c>
-      <c r="N2" t="n">
-        <v>41</v>
-      </c>
-      <c r="O2" t="n">
-        <v>57</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.3607594936708861</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>6</v>
-      </c>
       <c r="R2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1329113924050633</v>
+        <v>0.0782122905027933</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U2" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1075949367088608</v>
+        <v>0.07262569832402235</v>
       </c>
       <c r="W2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="X2" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1962025316455696</v>
+        <v>0.1620111731843575</v>
       </c>
       <c r="Z2" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="AA2" t="n">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2025316455696203</v>
+        <v>0.2486033519553073</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7192982456140351</v>
+        <v>0.5414012738853503</v>
       </c>
       <c r="AD2" t="n">
         <v>0.2857142857142857</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.28125</v>
+        <v>0.3707865168539326</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.43859649122807</v>
+        <v>1.082802547770701</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9591836734693877</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.4848484848484849</v>
+        <v>0.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.6629213483146067</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.666666666666667</v>
+        <v>1.7</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.380952380952381</v>
+        <v>1.173333333333333</v>
       </c>
       <c r="AO2" t="n">
-        <v>7.523809523809524</v>
+        <v>4.773333333333333</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.904761904761905</v>
+        <v>5.946666666666666</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>82.94</v>
+        <v>82.79199999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>82.56</v>
+        <v>82.91200000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>119.9127906976744</v>
+        <v>110.9610189116171</v>
       </c>
       <c r="E3" t="n">
-        <v>95.08236434108527</v>
+        <v>96.48784253184098</v>
       </c>
       <c r="F3" t="n">
+        <v>0.4818435754189945</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.14911722602195</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3938053097345133</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3212290502793296</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L3" t="n">
+        <v>17</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>17</v>
+      </c>
+      <c r="O3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.4385474860335196</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.0782122905027933</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.07262569832402235</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.1620111731843575</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2486033519553073</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5414012738853503</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.3707865168539325</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.082802547770701</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.9591836734693877</v>
+      </c>
+      <c r="AK3" t="n">
         <v>0.5</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.1040221914008322</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.4044943820224719</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.2531645569620253</v>
-      </c>
-      <c r="J3" t="n">
-        <v>8</v>
-      </c>
-      <c r="K3" t="n">
-        <v>16</v>
-      </c>
-      <c r="L3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>4</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.3607594936708861</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.1329113924050633</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.1075949367088608</v>
-      </c>
-      <c r="W3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.1962025316455696</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.2025316455696203</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.7192982456140351</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.2903225806451613</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.28125</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.43859649122807</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.4848484848484849</v>
-      </c>
       <c r="AL3" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.6629213483146068</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.666666666666667</v>
+        <v>1.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.380952380952381</v>
+        <v>1.173333333333333</v>
       </c>
       <c r="AO3" t="n">
-        <v>7.523809523809524</v>
+        <v>4.773333333333333</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.904761904761905</v>
+        <v>5.946666666666666</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>164.36</v>
+        <v>415.16</v>
       </c>
       <c r="C4" t="n">
-        <v>165.12</v>
+        <v>414.56</v>
       </c>
       <c r="D4" t="n">
-        <v>95.08236434108527</v>
+        <v>96.48784253184098</v>
       </c>
       <c r="E4" t="n">
-        <v>119.9127906976744</v>
+        <v>110.9610189116171</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4413793103448276</v>
+        <v>0.444</v>
       </c>
       <c r="G4" t="n">
-        <v>0.167207134171058</v>
+        <v>0.1343757634986562</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.3206751054852321</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2</v>
+        <v>0.1786666666666667</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="M4" t="n">
+        <v>27</v>
+      </c>
+      <c r="N4" t="n">
+        <v>98</v>
+      </c>
+      <c r="O4" t="n">
+        <v>181</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4826666666666667</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>33</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>27</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="W4" t="n">
         <v>12</v>
       </c>
-      <c r="N4" t="n">
-        <v>30</v>
-      </c>
-      <c r="O4" t="n">
-        <v>56</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.3862068965517241</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>7</v>
-      </c>
-      <c r="R4" t="n">
-        <v>21</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1448275862068966</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>13</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.0896551724137931</v>
-      </c>
-      <c r="W4" t="n">
-        <v>5</v>
-      </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09655172413793103</v>
+        <v>0.1066666666666667</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2827586206896552</v>
+        <v>0.2506666666666666</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5414364640883977</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.2872340425531915</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.071428571428571</v>
+        <v>1.082872928176795</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9818181818181818</v>
+        <v>0.8731343283582089</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.4133333333333333</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6710526315789473</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.071428571428572</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.5757575757575758</v>
+        <v>1.151515151515152</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.393939393939394</v>
+        <v>5.681818181818182</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.96969696969697</v>
+        <v>6.833333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82.18000000000001</v>
+        <v>83.03200000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>82.56</v>
+        <v>82.91200000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>95.08236434108527</v>
+        <v>96.48784253184098</v>
       </c>
       <c r="E5" t="n">
-        <v>119.9127906976744</v>
+        <v>110.9610189116171</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4413793103448276</v>
+        <v>0.444</v>
       </c>
       <c r="G5" t="n">
-        <v>0.167207134171058</v>
+        <v>0.1343757634986562</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.320675105485232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2</v>
+        <v>0.1786666666666667</v>
       </c>
       <c r="J5" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="L5" t="n">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="N5" t="n">
-        <v>15</v>
+        <v>19.6</v>
       </c>
       <c r="O5" t="n">
-        <v>28</v>
+        <v>36.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3862068965517241</v>
+        <v>0.4826666666666667</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1448275862068966</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U5" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0896551724137931</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09655172413793103</v>
+        <v>0.1066666666666667</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
+        <v>18.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2827586206896552</v>
+        <v>0.2506666666666666</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5414364640883977</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2424242424242425</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.2872340425531915</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.071428571428571</v>
+        <v>1.082872928176795</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9818181818181818</v>
+        <v>0.873134328358209</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.4133333333333333</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6710526315789473</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.071428571428572</v>
+        <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.5757575757575758</v>
+        <v>1.151515151515152</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.393939393939394</v>
+        <v>5.681818181818183</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.96969696969697</v>
+        <v>6.833333333333334</v>
       </c>
     </row>
     <row r="7">
@@ -1429,106 +1429,106 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
+        <v>11</v>
+      </c>
+      <c r="H8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I8" t="n">
+        <v>13</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>12</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>13</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>45</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>10</v>
+      </c>
+      <c r="X8" t="n">
         <v>7</v>
       </c>
-      <c r="H8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>31</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>6</v>
-      </c>
-      <c r="X8" t="n">
-        <v>5</v>
-      </c>
       <c r="Y8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>0.632</v>
       </c>
       <c r="AB8" t="n">
         <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.4</v>
+        <v>0.444</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -1537,54 +1537,54 @@
         <v>1</v>
       </c>
       <c r="AL8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.143</v>
+        <v>0.1</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>48:33</t>
+          <t>110:56</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>29.4</v>
+        <v>62.72</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.452</v>
+        <v>0.433</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.551</v>
+        <v>0.493</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.952</v>
+        <v>0.797</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.136</v>
+        <v>0.191</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.429</v>
+        <v>0.244</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.5</v>
+        <v>1.833</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.75</v>
+        <v>5.583</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.24</v>
+        <v>0.225</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.056</v>
+        <v>0.032</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.146</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.098</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="9">
@@ -1594,61 +1594,61 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q9" t="n">
         <v>5</v>
       </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="U9" t="n">
         <v>1</v>
@@ -1657,25 +1657,25 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
+        <v>4</v>
+      </c>
+      <c r="X9" t="n">
         <v>2</v>
       </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1684,72 +1684,72 @@
         <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
         <v>3</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1</v>
-      </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31:52</t>
+          <t>70:00</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>15.88</v>
+        <v>39.64</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.143</v>
+        <v>0.138</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.168</v>
+        <v>0.19</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.315</v>
+        <v>0.303</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.063</v>
+        <v>0.202</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.138</v>
       </c>
       <c r="AU9" t="n">
-        <v>4</v>
+        <v>0.875</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>3.625</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>4.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.197</v>
+        <v>0.225</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.028</v>
+        <v>0.038</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.059</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="10">
@@ -1759,67 +1759,67 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="C10" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="U10" t="n">
         <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1828,22 +1828,22 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AC10" t="n">
         <v>3</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AD10" t="n">
         <v>0.667</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.5</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -1867,54 +1867,54 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>30:46</t>
+          <t>87:52</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>9.44</v>
+        <v>23.64</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.429</v>
+        <v>0.412</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.47</v>
+        <v>0.433</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.742</v>
+        <v>0.719</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.212</v>
+        <v>0.169</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.143</v>
+        <v>0.176</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AW10" t="n">
-        <v>4</v>
+        <v>8.25</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.122</v>
+        <v>0.107</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.058</v>
+        <v>0.106</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.015</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="11">
@@ -1924,16 +1924,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1942,19 +1942,19 @@
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1966,25 +1966,25 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>2</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-1</v>
-      </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11" t="n">
         <v>4</v>
@@ -1993,13 +1993,13 @@
         <v>3</v>
       </c>
       <c r="Y11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -2039,47 +2039,47 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>28:20</t>
+          <t>55:37</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>13.2</v>
+        <v>27.6</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.2</v>
+        <v>0.294</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.369</v>
+        <v>0.466</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.797</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.076</v>
+        <v>0.145</v>
       </c>
       <c r="AT11" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="AU11" t="n">
         <v>0.5</v>
       </c>
-      <c r="AU11" t="n">
-        <v>1</v>
-      </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>4.25</v>
       </c>
       <c r="AW11" t="n">
-        <v>11</v>
+        <v>4.75</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.185</v>
+        <v>0.197</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="12">
@@ -2089,91 +2089,91 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" t="n">
         <v>6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="U12" t="n">
         <v>3</v>
       </c>
       <c r="V12" t="n">
+        <v>11</v>
+      </c>
+      <c r="W12" t="n">
+        <v>18</v>
+      </c>
+      <c r="X12" t="n">
         <v>7</v>
       </c>
-      <c r="W12" t="n">
-        <v>9</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4</v>
-      </c>
       <c r="Y12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.625</v>
+        <v>0.714</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2188,63 +2188,63 @@
         <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.4</v>
+        <v>0.471</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>25:37</t>
+          <t>83:15</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>18.88</v>
+        <v>46.96</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.583</v>
+        <v>0.654</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.583</v>
+        <v>0.64</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.165</v>
+        <v>1.171</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.056</v>
+        <v>0.103</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.292</v>
+        <v>0.224</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.211</v>
+        <v>0.117</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.243</v>
+        <v>0.203</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="13">
@@ -2254,37 +2254,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" t="n">
+        <v>21</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13</v>
+      </c>
+      <c r="L13" t="n">
         <v>6</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>13</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
       </c>
       <c r="M13" t="n">
         <v>3</v>
@@ -2296,40 +2296,40 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.75</v>
+        <v>0.545</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2350,66 +2350,66 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AK13" t="n">
         <v>4</v>
       </c>
-      <c r="AI13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1</v>
-      </c>
       <c r="AL13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.167</v>
+        <v>0.4</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>44:47</t>
+          <t>92:47</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>21.76</v>
+        <v>46.24</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.553</v>
+        <v>0.609</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.602</v>
+        <v>0.715</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.149</v>
+        <v>1.276</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.046</v>
+        <v>0.108</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.211</v>
+        <v>0.625</v>
       </c>
       <c r="AU13" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.193</v>
+        <v>0.198</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.08</v>
+        <v>0.057</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.079</v>
+        <v>0.118</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.081</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="14">
@@ -2419,82 +2419,82 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" t="n">
+        <v>37</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>18</v>
+      </c>
+      <c r="I14" t="n">
+        <v>27</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>17</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>11</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>45</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6</v>
+      </c>
+      <c r="W14" t="n">
         <v>12</v>
       </c>
-      <c r="E14" t="n">
-        <v>19</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="X14" t="n">
         <v>8</v>
       </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>32</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.647</v>
+        <v>0.471</v>
       </c>
       <c r="AB14" t="n">
         <v>1</v>
@@ -2506,75 +2506,75 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>104:55</t>
+        </is>
+      </c>
+      <c r="AO14" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AU14" t="n">
         <v>2</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>47:43</t>
-        </is>
-      </c>
-      <c r="AO14" t="n">
-        <v>24.52</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.223</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.204</v>
+        <v>0.216</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.075</v>
+        <v>0.118</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.13</v>
+        <v>0.137</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="15">
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>02:28</t>
+          <t>02:49</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.161</v>
+        <v>0.141</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -2749,67 +2749,67 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
         <v>11</v>
       </c>
-      <c r="H16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
+        <v>8</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
         <v>7</v>
@@ -2818,93 +2818,93 @@
         <v>4</v>
       </c>
       <c r="Y16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="AA16" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1</v>
       </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AK16" t="n">
         <v>6</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2</v>
-      </c>
       <c r="AL16" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>39:49</t>
+          <t>122:36</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>17.32</v>
+        <v>62.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.536</v>
+        <v>0.429</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.587</v>
+        <v>0.459</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.039</v>
+        <v>0.785</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.115</v>
+        <v>0.144</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.214</v>
+        <v>0.143</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="AV16" t="n">
-        <v>7</v>
+        <v>5.444</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.172</v>
+        <v>0.202</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.045</v>
+        <v>0.058</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.089</v>
+        <v>0.076</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.016</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="17">
@@ -2914,82 +2914,82 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>49</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13</v>
+      </c>
+      <c r="E17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" t="n">
+        <v>13</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>15</v>
+      </c>
+      <c r="L17" t="n">
+        <v>19</v>
+      </c>
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="C17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D17" t="n">
-        <v>6</v>
-      </c>
-      <c r="E17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="N17" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="n">
+      <c r="O17" t="n">
         <v>3</v>
       </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
         <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W17" t="n">
+        <v>8</v>
+      </c>
+      <c r="X17" t="n">
         <v>5</v>
       </c>
-      <c r="X17" t="n">
-        <v>3</v>
-      </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.714</v>
+        <v>0.571</v>
       </c>
       <c r="AB17" t="n">
         <v>1</v>
@@ -3010,66 +3010,66 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="n">
         <v>2</v>
       </c>
-      <c r="AI17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41:13</t>
+          <t>121:22</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>15.88</v>
+        <v>41.72</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.655</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.842</v>
+        <v>0.706</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.259</v>
+        <v>1.174</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.252</v>
+        <v>0.168</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.182</v>
+        <v>0.379</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.75</v>
+        <v>1.143</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.75</v>
+        <v>4.143</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.5</v>
+        <v>5.286</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.153</v>
+        <v>0.137</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.139</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.048</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="18">
@@ -3079,40 +3079,40 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" t="n">
         <v>2</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
         <v>7</v>
       </c>
-      <c r="D18" t="n">
+      <c r="G18" t="n">
+        <v>23</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>8</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
@@ -3121,19 +3121,19 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
@@ -3142,25 +3142,25 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3169,72 +3169,72 @@
         <v>1</v>
       </c>
       <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1</v>
       </c>
-      <c r="AG18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
       <c r="AI18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AL18" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>53:03</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>13.32</v>
+        <v>33.64</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.278</v>
+        <v>0.463</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.339</v>
+        <v>0.506</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.526</v>
+        <v>0.892</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.225</v>
+        <v>0.119</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.222</v>
+        <v>0.185</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AV18" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="AW18" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.262</v>
+        <v>0.252</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.132</v>
+        <v>0.159</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.044</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="19">
@@ -3244,162 +3244,162 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>63</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19</v>
+      </c>
+      <c r="H19" t="n">
+        <v>20</v>
+      </c>
+      <c r="I19" t="n">
+        <v>33</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="C19" t="n">
-        <v>27</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="K19" t="n">
+        <v>36</v>
+      </c>
+      <c r="L19" t="n">
+        <v>7</v>
+      </c>
+      <c r="M19" t="n">
         <v>6</v>
       </c>
-      <c r="E19" t="n">
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>18</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>62</v>
+      </c>
+      <c r="U19" t="n">
         <v>7</v>
       </c>
-      <c r="F19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" t="n">
-        <v>6</v>
-      </c>
-      <c r="H19" t="n">
-        <v>6</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>12</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="W19" t="n">
+        <v>4</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y19" t="n">
         <v>7</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>29</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
+      <c r="Z19" t="n">
         <v>10</v>
       </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5</v>
-      </c>
       <c r="AA19" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AB19" t="n">
         <v>1</v>
       </c>
       <c r="AC19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>2</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AI19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1</v>
-      </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AL19" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>38:44</t>
+          <t>94:48</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>21.28</v>
+        <v>56.52</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.652</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.739</v>
+        <v>0.663</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.269</v>
+        <v>1.115</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.141</v>
+        <v>0.159</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.462</v>
+        <v>0.606</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.333</v>
+        <v>3.667</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.667</v>
+        <v>3.889</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.218</v>
+        <v>0.237</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.116</v>
+        <v>0.065</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.275</v>
+        <v>0.32</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="20">
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3436,25 +3436,25 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>4</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -3574,159 +3574,159 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>198</v>
+        <v>460</v>
       </c>
       <c r="D21" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="E21" t="n">
-        <v>95</v>
+        <v>211</v>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>63</v>
+        <v>147</v>
       </c>
       <c r="H21" t="n">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="I21" t="n">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="J21" t="n">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="K21" t="n">
-        <v>57</v>
+        <v>161</v>
       </c>
       <c r="L21" t="n">
+        <v>89</v>
+      </c>
+      <c r="M21" t="n">
+        <v>39</v>
+      </c>
+      <c r="N21" t="n">
+        <v>15</v>
+      </c>
+      <c r="O21" t="n">
+        <v>14</v>
+      </c>
+      <c r="P21" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q21" t="n">
         <v>36</v>
       </c>
-      <c r="M21" t="n">
-        <v>21</v>
-      </c>
-      <c r="N21" t="n">
-        <v>6</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>121</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>372</v>
+      </c>
+      <c r="U21" t="n">
+        <v>33</v>
+      </c>
+      <c r="V21" t="n">
+        <v>59</v>
+      </c>
+      <c r="W21" t="n">
+        <v>85</v>
+      </c>
+      <c r="X21" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>157</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="AB21" t="n">
         <v>8</v>
       </c>
-      <c r="R21" t="n">
-        <v>48</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>169</v>
-      </c>
-      <c r="U21" t="n">
-        <v>16</v>
-      </c>
-      <c r="V21" t="n">
-        <v>32</v>
-      </c>
-      <c r="W21" t="n">
-        <v>35</v>
-      </c>
-      <c r="X21" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>41</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>6</v>
-      </c>
       <c r="AC21" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AD21" t="n">
         <v>0.286</v>
       </c>
       <c r="AE21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AF21" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.294</v>
+        <v>0.346</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AI21" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.29</v>
+        <v>0.241</v>
       </c>
       <c r="AK21" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="AL21" t="n">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.281</v>
+        <v>0.371</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>400:00</t>
+          <t>1000:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>201.88</v>
+        <v>502.96</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.5</v>
+        <v>0.482</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.547</v>
+        <v>0.537</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.981</v>
+        <v>0.915</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.104</v>
+        <v>0.149</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.253</v>
+        <v>0.321</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.381</v>
+        <v>1.173</v>
       </c>
       <c r="AV21" t="n">
-        <v>7.524</v>
+        <v>4.773</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.904999999999999</v>
+        <v>5.947</v>
       </c>
       <c r="AX21" t="n">
         <v>0.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.127</v>
+        <v>0.136</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -3739,159 +3739,159 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>400</v>
+      </c>
+      <c r="D22" t="n">
+        <v>108</v>
+      </c>
+      <c r="E22" t="n">
+        <v>241</v>
+      </c>
+      <c r="F22" t="n">
+        <v>39</v>
+      </c>
+      <c r="G22" t="n">
+        <v>134</v>
+      </c>
+      <c r="H22" t="n">
+        <v>67</v>
+      </c>
+      <c r="I22" t="n">
+        <v>114</v>
+      </c>
+      <c r="J22" t="n">
+        <v>76</v>
+      </c>
+      <c r="K22" t="n">
+        <v>137</v>
+      </c>
+      <c r="L22" t="n">
+        <v>76</v>
+      </c>
+      <c r="M22" t="n">
+        <v>39</v>
+      </c>
+      <c r="N22" t="n">
+        <v>11</v>
+      </c>
+      <c r="O22" t="n">
+        <v>12</v>
+      </c>
+      <c r="P22" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>27</v>
+      </c>
+      <c r="R22" t="n">
+        <v>129</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>231</v>
+      </c>
+      <c r="U22" t="n">
+        <v>31</v>
+      </c>
+      <c r="V22" t="n">
+        <v>51</v>
+      </c>
+      <c r="W22" t="n">
+        <v>68</v>
+      </c>
+      <c r="X22" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>98</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>181</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="AE22" t="n">
         <v>2</v>
       </c>
-      <c r="C22" t="n">
-        <v>157</v>
-      </c>
-      <c r="D22" t="n">
-        <v>37</v>
-      </c>
-      <c r="E22" t="n">
-        <v>90</v>
-      </c>
-      <c r="F22" t="n">
-        <v>18</v>
-      </c>
-      <c r="G22" t="n">
-        <v>55</v>
-      </c>
-      <c r="H22" t="n">
-        <v>29</v>
-      </c>
-      <c r="I22" t="n">
-        <v>44</v>
-      </c>
-      <c r="J22" t="n">
-        <v>19</v>
-      </c>
-      <c r="K22" t="n">
-        <v>53</v>
-      </c>
-      <c r="L22" t="n">
-        <v>33</v>
-      </c>
-      <c r="M22" t="n">
-        <v>13</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>5</v>
-      </c>
-      <c r="P22" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="AF22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AH22" t="n">
         <v>12</v>
       </c>
-      <c r="R22" t="n">
-        <v>48</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>74</v>
-      </c>
-      <c r="U22" t="n">
-        <v>13</v>
-      </c>
-      <c r="V22" t="n">
-        <v>24</v>
-      </c>
-      <c r="W22" t="n">
-        <v>29</v>
-      </c>
-      <c r="X22" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>5</v>
-      </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.357</v>
+        <v>0.3</v>
       </c>
       <c r="AK22" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.317</v>
+        <v>0.287</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>400:00</t>
+          <t>1000:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>197.36</v>
+        <v>491.16</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.441</v>
+        <v>0.444</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.478</v>
+        <v>0.47</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.796</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.167</v>
+        <v>0.134</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.2</v>
+        <v>0.179</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.576</v>
+        <v>1.152</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.394</v>
+        <v>5.682</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.97</v>
+        <v>6.833</v>
       </c>
       <c r="AX22" t="n">
         <v>0.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.073</v>
+        <v>0.064</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.119</v>
+        <v>0.121</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -3963,162 +3963,162 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>45</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W24" t="n">
         <v>2</v>
       </c>
-      <c r="C24" t="n">
-        <v>14</v>
-      </c>
-      <c r="D24" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>7</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I24" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="X24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>31</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AM24" t="n">
-        <v>0.143</v>
+        <v>0.1</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>24:16</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>14.7</v>
+        <v>12.544</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.452</v>
+        <v>0.433</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.551</v>
+        <v>0.493</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.952</v>
+        <v>0.797</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.136</v>
+        <v>0.191</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.429</v>
+        <v>0.244</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.5</v>
+        <v>1.833</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.75</v>
+        <v>5.583</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.24</v>
+        <v>0.225</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.056</v>
+        <v>0.032</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.146</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.098</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="25">
@@ -4128,106 +4128,106 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-12</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z25" t="n">
         <v>2</v>
       </c>
-      <c r="C25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1</v>
-      </c>
       <c r="AA25" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AJ25" t="n">
         <v>0</v>
@@ -4236,54 +4236,54 @@
         <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AM25" t="n">
         <v>0</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>7.94</v>
+        <v>7.928</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.143</v>
+        <v>0.138</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.168</v>
+        <v>0.19</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.315</v>
+        <v>0.303</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.063</v>
+        <v>0.202</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.138</v>
       </c>
       <c r="AU25" t="n">
-        <v>4</v>
+        <v>0.875</v>
       </c>
       <c r="AV25" t="n">
-        <v>14</v>
+        <v>3.625</v>
       </c>
       <c r="AW25" t="n">
-        <v>18</v>
+        <v>4.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.197</v>
+        <v>0.225</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.028</v>
+        <v>0.038</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="BA25" t="n">
-        <v>0.059</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="26">
@@ -4293,40 +4293,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E26" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4335,25 +4335,25 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4365,25 +4365,25 @@
         <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD26" t="n">
         <v>0.667</v>
       </c>
-      <c r="AB26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
@@ -4401,54 +4401,54 @@
         <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM26" t="n">
         <v>0</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>4.72</v>
+        <v>4.728</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.429</v>
+        <v>0.412</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.47</v>
+        <v>0.433</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.742</v>
+        <v>0.719</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.212</v>
+        <v>0.169</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.143</v>
+        <v>0.176</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AW26" t="n">
-        <v>4</v>
+        <v>8.25</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.122</v>
+        <v>0.107</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.058</v>
+        <v>0.106</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.015</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="27">
@@ -4458,37 +4458,37 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H27" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -4500,120 +4500,120 @@
         <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="X27" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="Y27" t="n">
         <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AO27" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="AU27" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AO27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0.6820000000000001</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>1</v>
-      </c>
       <c r="AV27" t="n">
-        <v>10</v>
+        <v>4.25</v>
       </c>
       <c r="AW27" t="n">
-        <v>11</v>
+        <v>4.75</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.185</v>
+        <v>0.197</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="28">
@@ -4623,162 +4623,162 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
         <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K28" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="V28" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="W28" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="X28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y28" t="n">
         <v>2</v>
       </c>
-      <c r="Y28" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Z28" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.625</v>
+        <v>0.714</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AG28" t="n">
         <v>0.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.4</v>
+        <v>0.471</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>9.44</v>
+        <v>9.391999999999999</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.583</v>
+        <v>0.654</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.583</v>
+        <v>0.64</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.165</v>
+        <v>1.171</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.056</v>
+        <v>0.103</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.292</v>
+        <v>0.224</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.211</v>
+        <v>0.117</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.243</v>
+        <v>0.203</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="29">
@@ -4788,162 +4788,162 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>47</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AL29" t="n">
         <v>2</v>
       </c>
-      <c r="C29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>22</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>2</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>3</v>
-      </c>
       <c r="AM29" t="n">
-        <v>0.167</v>
+        <v>0.4</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>22:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>10.88</v>
+        <v>9.247999999999999</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.553</v>
+        <v>0.609</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.602</v>
+        <v>0.715</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.149</v>
+        <v>1.276</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.046</v>
+        <v>0.108</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.211</v>
+        <v>0.625</v>
       </c>
       <c r="AU29" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.193</v>
+        <v>0.198</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.08</v>
+        <v>0.057</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.079</v>
+        <v>0.118</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.081</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="30">
@@ -4953,106 +4953,106 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>15</v>
+        <v>10.8</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="E30" t="n">
-        <v>9.5</v>
+        <v>7.4</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="n">
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="M30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>6</v>
+      </c>
+      <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="X30" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.647</v>
+        <v>0.471</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AF30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG30" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
       <c r="AH30" t="n">
         <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
@@ -5068,47 +5068,47 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>23:51</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>12.26</v>
+        <v>11.376</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.571</v>
+        <v>0.45</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.612</v>
+        <v>0.52</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.223</v>
+        <v>0.949</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.286</v>
+        <v>0.45</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.204</v>
+        <v>0.216</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.075</v>
+        <v>0.118</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.13</v>
+        <v>0.137</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="31">
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AJ31" t="n">
         <v>0</v>
@@ -5233,11 +5233,11 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>01:14</t>
+          <t>00:33</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AP31" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
         <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.161</v>
+        <v>0.141</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -5283,162 +5283,162 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I32" t="n">
         <v>2</v>
       </c>
-      <c r="C32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.5</v>
-      </c>
       <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>22</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>11</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
       <c r="AH32" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI32" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>24:31</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>8.66</v>
+        <v>12.48</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.536</v>
+        <v>0.429</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.587</v>
+        <v>0.459</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.039</v>
+        <v>0.785</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.115</v>
+        <v>0.144</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.214</v>
+        <v>0.143</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="AV32" t="n">
-        <v>7</v>
+        <v>5.444</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.172</v>
+        <v>0.202</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.045</v>
+        <v>0.058</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.089</v>
+        <v>0.076</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.016</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="33">
@@ -5448,88 +5448,88 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K33" t="n">
         <v>3</v>
       </c>
-      <c r="E33" t="n">
-        <v>4</v>
-      </c>
-      <c r="F33" t="n">
+      <c r="L33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="G33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H33" t="n">
+      <c r="R33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>50</v>
+      </c>
+      <c r="U33" t="n">
         <v>1</v>
       </c>
-      <c r="I33" t="n">
+      <c r="V33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" t="n">
-        <v>2</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>16</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Y33" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.714</v>
+        <v>0.571</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AD33" t="n">
         <v>1</v>
@@ -5544,66 +5544,66 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AI33" t="n">
         <v>1</v>
       </c>
-      <c r="AI33" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>24:16</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>7.94</v>
+        <v>8.343999999999999</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.655</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.842</v>
+        <v>0.706</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.259</v>
+        <v>1.174</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.252</v>
+        <v>0.168</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.182</v>
+        <v>0.379</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.75</v>
+        <v>1.143</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.75</v>
+        <v>4.143</v>
       </c>
       <c r="AW33" t="n">
-        <v>3.5</v>
+        <v>5.286</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.153</v>
+        <v>0.137</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.139</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.048</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="34">
@@ -5613,162 +5613,162 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K34" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>23</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AA34" t="n">
         <v>1</v>
       </c>
-      <c r="N34" t="n">
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG34" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1</v>
-      </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>6.66</v>
+        <v>6.728</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.278</v>
+        <v>0.463</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.339</v>
+        <v>0.506</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.526</v>
+        <v>0.892</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.225</v>
+        <v>0.119</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.222</v>
+        <v>0.185</v>
       </c>
       <c r="AU34" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AV34" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="AW34" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.262</v>
+        <v>0.252</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.132</v>
+        <v>0.159</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.044</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="35">
@@ -5778,162 +5778,162 @@
         </is>
       </c>
       <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>62</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z35" t="n">
         <v>2</v>
       </c>
-      <c r="C35" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="D35" t="n">
+      <c r="AA35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL35" t="n">
         <v>3</v>
       </c>
-      <c r="E35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G35" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" t="n">
-        <v>3</v>
-      </c>
-      <c r="I35" t="n">
-        <v>6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>6</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>29</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AM35" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>10.64</v>
+        <v>11.304</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.652</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.739</v>
+        <v>0.663</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.269</v>
+        <v>1.115</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.141</v>
+        <v>0.159</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.462</v>
+        <v>0.606</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.333</v>
+        <v>3.667</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.667</v>
+        <v>3.889</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.218</v>
+        <v>0.237</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.116</v>
+        <v>0.065</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.275</v>
+        <v>0.32</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="36">
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -5970,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
@@ -5985,10 +5985,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -6108,118 +6108,118 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D37" t="n">
-        <v>26</v>
+        <v>20.4</v>
       </c>
       <c r="E37" t="n">
-        <v>47.5</v>
+        <v>42.2</v>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="G37" t="n">
-        <v>31.5</v>
+        <v>29.4</v>
       </c>
       <c r="H37" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I37" t="n">
-        <v>26</v>
+        <v>31.8</v>
       </c>
       <c r="J37" t="n">
-        <v>14.5</v>
+        <v>17.6</v>
       </c>
       <c r="K37" t="n">
-        <v>28.5</v>
+        <v>32.2</v>
       </c>
       <c r="L37" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="M37" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="N37" t="n">
         <v>3</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="P37" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="R37" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>169</v>
+        <v>372</v>
       </c>
       <c r="U37" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="V37" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="W37" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="X37" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y37" t="n">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="Z37" t="n">
-        <v>28.5</v>
+        <v>31.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.719</v>
+        <v>0.541</v>
       </c>
       <c r="AB37" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="AD37" t="n">
         <v>0.286</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>8.5</v>
+        <v>5.2</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.294</v>
+        <v>0.346</v>
       </c>
       <c r="AH37" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="AI37" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.29</v>
+        <v>0.241</v>
       </c>
       <c r="AK37" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AL37" t="n">
-        <v>16</v>
+        <v>17.8</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.281</v>
+        <v>0.371</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6227,40 +6227,40 @@
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>100.94</v>
+        <v>100.592</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.5</v>
+        <v>0.482</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.547</v>
+        <v>0.537</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.981</v>
+        <v>0.915</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.104</v>
+        <v>0.149</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.253</v>
+        <v>0.321</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.381</v>
+        <v>1.173</v>
       </c>
       <c r="AV37" t="n">
-        <v>7.524</v>
+        <v>4.773</v>
       </c>
       <c r="AW37" t="n">
-        <v>8.904999999999999</v>
+        <v>5.947</v>
       </c>
       <c r="AX37" t="n">
         <v>0.2</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.127</v>
+        <v>0.136</v>
       </c>
       <c r="BA37" t="n">
         <v>0</v>
@@ -6273,118 +6273,118 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>78.5</v>
+        <v>80</v>
       </c>
       <c r="D38" t="n">
-        <v>18.5</v>
+        <v>21.6</v>
       </c>
       <c r="E38" t="n">
-        <v>45</v>
+        <v>48.2</v>
       </c>
       <c r="F38" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="G38" t="n">
-        <v>27.5</v>
+        <v>26.8</v>
       </c>
       <c r="H38" t="n">
-        <v>14.5</v>
+        <v>13.4</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>22.8</v>
       </c>
       <c r="J38" t="n">
-        <v>9.5</v>
+        <v>15.2</v>
       </c>
       <c r="K38" t="n">
-        <v>26.5</v>
+        <v>27.4</v>
       </c>
       <c r="L38" t="n">
-        <v>16.5</v>
+        <v>15.2</v>
       </c>
       <c r="M38" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="O38" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P38" t="n">
-        <v>16.5</v>
+        <v>13.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="R38" t="n">
-        <v>24</v>
+        <v>25.8</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>74</v>
+        <v>231</v>
       </c>
       <c r="U38" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="V38" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="W38" t="n">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="X38" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>15</v>
+        <v>19.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>28</v>
+        <v>36.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.536</v>
+        <v>0.541</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.333</v>
+        <v>0.242</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.357</v>
+        <v>0.3</v>
       </c>
       <c r="AK38" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AL38" t="n">
-        <v>20.5</v>
+        <v>18.8</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.317</v>
+        <v>0.287</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
@@ -6392,40 +6392,40 @@
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>98.68000000000001</v>
+        <v>98.232</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.441</v>
+        <v>0.444</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.478</v>
+        <v>0.47</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.796</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.167</v>
+        <v>0.134</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.2</v>
+        <v>0.179</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.576</v>
+        <v>1.152</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.394</v>
+        <v>5.682</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.97</v>
+        <v>6.833</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.196</v>
+        <v>0.195</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.074</v>
+        <v>0.067</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.118</v>
+        <v>0.116</v>
       </c>
       <c r="BA38" t="n">
         <v>0</v>
